--- a/data/trans_dic/P16A08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,03</t>
+          <t>0,89; 3,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,57</t>
+          <t>1,18; 3,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,19</t>
+          <t>1,62; 4,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,04</t>
+          <t>1,81; 5,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,34</t>
+          <t>1,22; 3,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,27</t>
+          <t>3,06; 6,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,47</t>
+          <t>2,29; 5,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,11</t>
+          <t>2,93; 6,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,85</t>
+          <t>1,3; 2,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,36</t>
+          <t>2,42; 4,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,24</t>
+          <t>2,24; 4,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,97</t>
+          <t>2,83; 5,13</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,75</t>
+          <t>1,52; 3,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,01</t>
+          <t>2,52; 4,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,94</t>
+          <t>1,85; 4,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,47</t>
+          <t>1,27; 4,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,13</t>
+          <t>2,53; 4,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,29</t>
+          <t>4,48; 7,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,53</t>
+          <t>4,41; 7,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,0</t>
+          <t>2,65; 4,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,93</t>
+          <t>2,33; 4,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,68</t>
+          <t>3,69; 5,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,32</t>
+          <t>3,49; 5,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,09</t>
+          <t>2,08; 4,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,66</t>
+          <t>1,25; 3,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,26</t>
+          <t>2,62; 5,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,66</t>
+          <t>1,93; 4,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,77</t>
+          <t>3,01; 6,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,2</t>
+          <t>2,97; 6,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,97</t>
+          <t>4,03; 7,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,94</t>
+          <t>5,37; 9,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,68</t>
+          <t>2,0; 5,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,56</t>
+          <t>2,38; 4,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,11</t>
+          <t>3,86; 6,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,09</t>
+          <t>3,98; 6,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,39</t>
+          <t>2,63; 5,57</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,44</t>
+          <t>2,0; 4,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,93</t>
+          <t>2,5; 5,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,89</t>
+          <t>2,55; 5,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,53</t>
+          <t>1,95; 4,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 6,44</t>
+          <t>3,78; 6,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,4</t>
+          <t>4,39; 7,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,47</t>
+          <t>3,71; 6,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 28,01</t>
+          <t>5,29; 29,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 5,12</t>
+          <t>3,18; 4,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,78</t>
+          <t>3,79; 5,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,32</t>
+          <t>3,35; 5,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 20,24</t>
+          <t>4,09; 19,34</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,01</t>
+          <t>1,86; 2,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,12</t>
+          <t>2,78; 4,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,7</t>
+          <t>2,51; 3,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,14</t>
+          <t>2,42; 4,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,59</t>
+          <t>3,27; 4,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 6,35</t>
+          <t>4,74; 6,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,2</t>
+          <t>4,68; 6,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,18; 12,66</t>
+          <t>4,21; 13,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,64</t>
+          <t>2,74; 3,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,02</t>
+          <t>4,02; 5,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 4,77</t>
+          <t>3,78; 4,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,79</t>
+          <t>3,7; 8,08</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas</t>
+          <t>Población que ha consumido medicamentos para la alergia en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6601; 21008</t>
+          <t>6199; 20974</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8950; 24997</t>
+          <t>8292; 24928</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11203; 28296</t>
+          <t>10960; 29540</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11491; 32017</t>
+          <t>11476; 32674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8637; 22966</t>
+          <t>8376; 23508</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21106; 43444</t>
+          <t>21199; 42219</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15201; 36821</t>
+          <t>15395; 34913</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20342; 41266</t>
+          <t>19820; 41194</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17928; 39387</t>
+          <t>17961; 38884</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33857; 60756</t>
+          <t>33771; 60552</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30216; 57175</t>
+          <t>30221; 56316</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37708; 65094</t>
+          <t>37128; 67227</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14725; 36091</t>
+          <t>14662; 35447</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24547; 50989</t>
+          <t>25646; 49620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19039; 40327</t>
+          <t>18960; 41899</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15983; 53307</t>
+          <t>15187; 53261</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24649; 49722</t>
+          <t>24500; 47970</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45849; 74832</t>
+          <t>45987; 77382</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46440; 78508</t>
+          <t>45947; 77188</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26191; 47886</t>
+          <t>25406; 47097</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44987; 75788</t>
+          <t>44966; 77664</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>76216; 116226</t>
+          <t>75511; 118781</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70360; 109848</t>
+          <t>72181; 111711</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44566; 87919</t>
+          <t>44818; 90186</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8275; 24848</t>
+          <t>8476; 25955</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20197; 47327</t>
+          <t>19835; 44459</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14659; 35395</t>
+          <t>14693; 33582</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21615; 47612</t>
+          <t>21159; 47036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20535; 42412</t>
+          <t>20298; 41739</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32079; 61903</t>
+          <t>31253; 58176</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41226; 70162</t>
+          <t>42124; 71655</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19019; 52964</t>
+          <t>18658; 53066</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33158; 62066</t>
+          <t>32368; 59703</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57395; 93712</t>
+          <t>59157; 95976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60396; 94017</t>
+          <t>61519; 96026</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44996; 88193</t>
+          <t>43101; 91075</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18876; 41792</t>
+          <t>18845; 40213</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23321; 46570</t>
+          <t>23604; 48111</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23956; 45863</t>
+          <t>23883; 47883</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17858; 41998</t>
+          <t>18116; 42926</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37782; 66856</t>
+          <t>39282; 67369</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46999; 77595</t>
+          <t>46019; 76089</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38201; 67554</t>
+          <t>38712; 67764</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56246; 305673</t>
+          <t>57749; 325488</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64220; 101353</t>
+          <t>62936; 97885</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76242; 115234</t>
+          <t>75463; 114631</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>69076; 105460</t>
+          <t>66282; 104207</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82540; 408562</t>
+          <t>82567; 390387</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61545; 98468</t>
+          <t>61076; 96429</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97114; 140864</t>
+          <t>94908; 139426</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85287; 125454</t>
+          <t>85196; 126112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84475; 143314</t>
+          <t>83532; 141710</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110742; 154949</t>
+          <t>110391; 157218</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>169425; 224957</t>
+          <t>167870; 224586</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>163880; 219774</t>
+          <t>165895; 218225</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>152869; 463207</t>
+          <t>153989; 503983</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>180513; 242450</t>
+          <t>182254; 242954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>274781; 349313</t>
+          <t>279694; 352409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>259786; 330773</t>
+          <t>262087; 332000</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>261143; 625379</t>
+          <t>263416; 574729</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A08-Habitat-trans_dic.xlsx
@@ -664,39 +664,39 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>3,31%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>3,15%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,03</t>
+          <t>0,98; 2,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,56</t>
+          <t>1,25; 3,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,38</t>
+          <t>1,59; 4,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,15</t>
+          <t>2,03; 5,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,42</t>
+          <t>1,28; 3,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,09</t>
+          <t>3,03; 6,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,19</t>
+          <t>2,41; 5,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,1</t>
+          <t>3,06; 5,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,81</t>
+          <t>1,34; 2,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,34</t>
+          <t>2,47; 4,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,18</t>
+          <t>2,28; 4,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,13</t>
+          <t>2,8; 5,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,69</t>
+          <t>1,49; 3,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,87</t>
+          <t>2,55; 4,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,1</t>
+          <t>1,89; 4,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,46</t>
+          <t>2,13; 4,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,95</t>
+          <t>2,53; 5,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,54</t>
+          <t>4,41; 7,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,4</t>
+          <t>4,54; 7,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,92</t>
+          <t>2,84; 5,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,02</t>
+          <t>2,31; 3,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,81</t>
+          <t>3,68; 5,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 5,41</t>
+          <t>3,48; 5,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,19</t>
+          <t>2,68; 4,38</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,83</t>
+          <t>1,27; 3,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,88</t>
+          <t>2,63; 5,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,42</t>
+          <t>2,07; 4,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,68</t>
+          <t>3,0; 6,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,1</t>
+          <t>3,01; 6,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,49</t>
+          <t>4,14; 7,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 9,13</t>
+          <t>5,16; 8,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,69</t>
+          <t>4,55; 7,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,38</t>
+          <t>2,38; 4,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,26</t>
+          <t>3,81; 6,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,22</t>
+          <t>3,96; 6,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,57</t>
+          <t>4,15; 6,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,27</t>
+          <t>1,94; 4,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,1</t>
+          <t>2,52; 5,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,11</t>
+          <t>2,52; 5,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,63</t>
+          <t>2,0; 4,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,49</t>
+          <t>3,67; 6,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,26</t>
+          <t>4,49; 7,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,49</t>
+          <t>3,68; 6,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 29,82</t>
+          <t>4,61; 7,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,94</t>
+          <t>3,21; 4,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,75</t>
+          <t>3,88; 5,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,26</t>
+          <t>3,49; 5,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,09; 19,34</t>
+          <t>3,69; 5,42</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,94</t>
+          <t>1,89; 2,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,08</t>
+          <t>2,78; 4,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,72</t>
+          <t>2,57; 3,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,1</t>
+          <t>2,82; 4,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 4,65</t>
+          <t>3,32; 4,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,34</t>
+          <t>4,72; 6,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,16</t>
+          <t>4,62; 6,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,78</t>
+          <t>4,36; 5,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 3,65</t>
+          <t>2,73; 3,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,06</t>
+          <t>3,99; 5,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 4,78</t>
+          <t>3,77; 4,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,08</t>
+          <t>3,77; 4,68</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20989</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>31326</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50216</t>
+          <t>53469</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6199; 20974</t>
+          <t>6779; 19631</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8292; 24928</t>
+          <t>8777; 23523</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10960; 29540</t>
+          <t>10724; 27215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11476; 32674</t>
+          <t>14005; 36483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8376; 23508</t>
+          <t>8833; 23955</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21199; 42219</t>
+          <t>20989; 42634</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15395; 34913</t>
+          <t>16210; 36567</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19820; 41194</t>
+          <t>22431; 43234</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17961; 38884</t>
+          <t>18448; 37520</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33771; 60552</t>
+          <t>34415; 60284</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30221; 56316</t>
+          <t>30703; 56382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37128; 67227</t>
+          <t>39846; 71098</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>32897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>40438</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67216</t>
+          <t>73334</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14662; 35447</t>
+          <t>14326; 35458</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25646; 49620</t>
+          <t>25983; 49897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18960; 41899</t>
+          <t>19308; 42342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15187; 53261</t>
+          <t>22353; 49119</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24500; 47970</t>
+          <t>24459; 49589</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45987; 77382</t>
+          <t>45235; 76732</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45947; 77188</t>
+          <t>47396; 78562</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25406; 47097</t>
+          <t>30460; 53980</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44966; 77664</t>
+          <t>44633; 76488</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75511; 118781</t>
+          <t>75225; 115920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72181; 111711</t>
+          <t>71876; 110182</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44818; 90186</t>
+          <t>56790; 92757</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>34179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38088</t>
+          <t>48927</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69917</t>
+          <t>83106</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8476; 25955</t>
+          <t>8651; 25388</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19835; 44459</t>
+          <t>19929; 45277</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14693; 33582</t>
+          <t>15704; 35575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21159; 47036</t>
+          <t>24079; 51016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20298; 41739</t>
+          <t>20560; 41691</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31253; 58176</t>
+          <t>32159; 58191</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42124; 71655</t>
+          <t>40473; 69513</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18658; 53066</t>
+          <t>36963; 62364</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32368; 59703</t>
+          <t>32438; 59073</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59157; 95976</t>
+          <t>58418; 94572</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61519; 96026</t>
+          <t>61183; 95432</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43101; 91075</t>
+          <t>66947; 100619</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27584</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>127428</t>
+          <t>64231</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>155012</t>
+          <t>94558</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18845; 40213</t>
+          <t>18258; 41262</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23604; 48111</t>
+          <t>23781; 48138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23883; 47883</t>
+          <t>23624; 48362</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18116; 42926</t>
+          <t>19768; 43829</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39282; 67369</t>
+          <t>38144; 68022</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46019; 76089</t>
+          <t>47098; 78119</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38712; 67764</t>
+          <t>38413; 68447</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>57749; 325488</t>
+          <t>51442; 79802</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62936; 97885</t>
+          <t>63659; 98717</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75463; 114631</t>
+          <t>77246; 116441</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>66282; 104207</t>
+          <t>69210; 108752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82567; 390387</t>
+          <t>77801; 114244</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112679</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>229682</t>
+          <t>184921</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>342361</t>
+          <t>304467</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61076; 96429</t>
+          <t>61806; 97361</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94908; 139426</t>
+          <t>95064; 139924</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85196; 126112</t>
+          <t>87399; 125072</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>83532; 141710</t>
+          <t>99673; 146731</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110391; 157218</t>
+          <t>112128; 156802</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>167870; 224586</t>
+          <t>167255; 223801</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>165895; 218225</t>
+          <t>163853; 221970</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>153989; 503983</t>
+          <t>162551; 211185</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182254; 242954</t>
+          <t>181916; 238183</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>279694; 352409</t>
+          <t>278194; 348033</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>262087; 332000</t>
+          <t>261314; 327835</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>263416; 574729</t>
+          <t>273514; 339927</t>
         </is>
       </c>
     </row>
